--- a/docs/02_基本設計/01_機能・画面一覧/KF-BD-012_画面共通仕様書.xlsx
+++ b/docs/02_基本設計/01_機能・画面一覧/KF-BD-012_画面共通仕様書.xlsx
@@ -71,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -93,11 +93,44 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -117,6 +150,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -494,6 +528,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -502,6 +539,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -513,7 +552,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -526,7 +565,7 @@
           <t>KF-BD-012</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -536,10 +575,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -552,7 +591,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -565,8 +604,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -613,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -672,6 +713,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>共通レイアウトを AppLayout（ヘッダー＋メイン）に更新、紺基調の配色・アラート表示（error／ok／info）を追加。ログイン画面のレスポンシブ、401 での自動復帰、localStorage 保存、初期パスワード時の誘導を実装に合わせて修正（Pinia・左メニュー・sessionStorage の記述を削除）</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -685,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +776,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>ヘッダー（システム名・ログインユーザー名・ログアウト）＋左メニュー＋メインエリア</t>
+          <t>共通レイアウト（AppLayout）：ヘッダー（勤怠フロー／ホーム／パスワード変更／氏名・ロール／ログアウト）＋メインエリア。左メニューは設けない</t>
         </is>
       </c>
     </row>
@@ -724,7 +788,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>1280px以上のPCを想定（レスポンシブ対応はしない）</t>
+          <t>PC（1280px 以上）を基本とする。ログイン画面は 2 カラム（左：紹介／右：入力）で、幅 760px 未満では縦積みに切り替える</t>
         </is>
       </c>
     </row>
@@ -772,7 +836,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>項目直下に赤字でメッセージ。API失敗時は画面上部にバナー表示</t>
+          <t>項目直下に赤字でメッセージ。API 失敗時は画面上部（またはフォーム内）にエラーアラート（.alert-error：赤字・淡赤背景）を表示</t>
         </is>
       </c>
     </row>
@@ -796,7 +860,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>I-系メッセージを画面上部に3秒表示</t>
+          <t>I-系メッセージは成功アラート（.alert-ok：緑字・淡緑背景）で表示。補足案内は情報アラート（.alert-info：紺字・淡青背景）</t>
         </is>
       </c>
     </row>
@@ -809,6 +873,30 @@
       <c r="B10" s="8" t="inlineStr">
         <is>
           <t>API呼び出し中はボタンを非活性にし、二重送信を防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>配色</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>紺系を基調（社内ブランドの色調のみ参考。ロゴ等は使用しない）。navy-900 #0f1f3d／navy-700 #1b3566（ボタン・見出し）／navy-500 #2b57a7（ホバー・フォーカス）／navy-100 #e6edf8（淡色背景）／背景 #f4f6fa／文字 #1c2433／補助文字 #6b7690／枠線 #d5dbe8／エラー #c0392b・背景 #fdecea／成功 #1e7b4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>共通部品</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>ボタン：通常（.btn：紺）・補助（.btn-ghost：枠線のみ）。入力欄：枠線 #d5dbe8、フォーカス時に紺の枠。補助説明は .hint（12px・補助文字色）。角丸 8px</t>
         </is>
       </c>
     </row>
@@ -824,7 +912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1236,6 +1324,40 @@
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>※現行実装のヘッダーに出るメニューはホームとパスワード変更。他のメニューは各画面の実装時にヘッダーへ追加する。</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1290,7 +1412,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>401受信時にログイン画面へ遷移（メッセージ表示）</t>
+          <t>API が 401 を返したらログイン情報（トークン・利用者情報）を破棄してログイン画面へ自動で戻る（メッセージ表示）。トークン有効期間は 2 時間</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1424,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>メニュー非表示に加え、直接URLアクセス時は403画面（E-010）</t>
+          <t>メニュー非表示に加え、API は 403（E-010）を返す。権限エラー専用画面は未実装</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1436,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Vue Router。ロールをメタ情報に持ちガードで制御</t>
+          <t>Vue Router。ルートのメタ情報 requiresAuth で未ログインを /login へ誘導（ガード）。ロール別の画面制御は画面追加時に拡張する</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1448,19 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>ログイン情報はPinia。トークンはメモリ＋sessionStorage</t>
+          <t>Pinia は使わない。トークンと利用者情報（userId・name・role・mustChangePassword）は API クライアント（api/client.js）が localStorage に保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワードの利用者</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>mustChangePassword が true の間は /password（SCR-007）以外の認証必須画面へ入れず、/password へ誘導する（ルーターガード）。サーバー側での強制は未実装のため、API を直接呼べば他の機能も利用できる（既知の課題）</t>
         </is>
       </c>
     </row>

--- a/docs/02_基本設計/01_機能・画面一覧/KF-BD-012_画面共通仕様書.xlsx
+++ b/docs/02_基本設計/01_機能・画面一覧/KF-BD-012_画面共通仕様書.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,8 +75,13 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -126,11 +136,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -151,6 +162,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -575,7 +593,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -654,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -736,6 +754,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>実装（AppLayout・router・client.js・style.css・各ビュー）と照合。レイアウトを上部バー＋左メニュー（ロール別）に修正（旧『左メニューは設けない』を削除）。ロール別メニューを実装のメニュー項目・ルートに更新。画面制御（ロール不一致は /home、401 の扱い、サーバー側の強制パスワード変更）、一覧（ページングなし）、必須バッジ、確認ダイアログ・エラー表示の記述を実装に合わせて修正</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワード期間の左メニュー無効表示（透明度40%・クリック不可）と案内文を追加。必須バッジの表示（縦並びのラベルで文字幅に留める）を追記。状態バッジの色分けに承認ステップ「処理なし」・ユーザー状態を追記。休憩・離席の区間の表示形式を追記し、ロール別メニューの「申請」に SCR-109 を追加</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -749,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -776,7 +840,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>共通レイアウト（AppLayout）：ヘッダー（勤怠フロー／ホーム／パスワード変更／氏名・ロール／ログアウト）＋メインエリア。左メニューは設けない</t>
+          <t>共通レイアウト（AppLayout）：上部バー（勤怠フロー／通知ベル（未読件数バッジ。60 秒ごと・画面遷移ごとに更新）／氏名・ロール／パスワード変更／ログアウト）＋左メニュー（ロール別・幅 210px）＋本文（最大幅 1100px）。ログイン画面のみ AppLayout を使わない。初期パスワードの利用者（mustChangePassword=true）の間は、左メニューを無効表示にして案内文を出す（下記「メニューの無効表示」）</t>
         </is>
       </c>
     </row>
@@ -788,7 +852,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>PC（1280px 以上）を基本とする。ログイン画面は 2 カラム（左：紹介／右：入力）で、幅 760px 未満では縦積みに切り替える</t>
+          <t>PC を基本とする。900px 以下では左メニューをハンバーガー（☰）で開閉し、氏名・パスワード変更リンクを隠す。ログイン画面は 2 カラム（左：紹介／右：入力）で、幅 760px 未満では縦積みに切り替える。フォームは 700px 以下で 1 列</t>
         </is>
       </c>
     </row>
@@ -800,7 +864,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>日付：yyyy/MM/dd　時刻：HH:mm　日数：0.0</t>
+          <t>日付：yyyy/MM/dd　時刻：HH:mm　日数：0.0日　勤務・残業時間：H:MM（分から換算）　休憩・離席の区間：「休憩 HH:mm–HH:mm」「離席 HH:mm–HH:mm」（終了前は終了時刻の代わりに「継続中」。複数は区切って並べる）</t>
         </is>
       </c>
     </row>
@@ -812,7 +876,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>1ページ20件。0件時は「該当するデータはありません。」を表示</t>
+          <t>ページングなし（全件を表示）。通知のみ最新 50 件。0件時は一覧ごとの文言を表示（「申請はありません。」「承認待ちの申請はありません。」「通知はありません。」「この月の打刻はありません。」など）</t>
         </is>
       </c>
     </row>
@@ -824,19 +888,19 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>ラベル横に赤い「*」を表示</t>
+          <t>ラベル横に赤地白文字の「必須」バッジ（.req：11px・太字・角丸4px）を表示する。ラベルとバッジを横に並べる箇所では左に余白6pxを付ける。縦並びのラベル（.field）の中では、バッジの幅を文字幅に留めて左寄せにし（.field &gt; .req：align-self flex-start・左余白なし）、横いっぱいに伸ばさない</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>エラー表示</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>項目直下に赤字でメッセージ。API 失敗時は画面上部（またはフォーム内）にエラーアラート（.alert-error：赤字・淡赤背景）を表示</t>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>API 失敗・入力不足は画面上部（またはフォーム内）にエラーアラート（.alert-error：赤字・淡赤背景）で 1 件表示する。API の fieldErrors は先頭のメッセージのみ表示（項目直下への表示は未実装）。確認ダイアログのコメント未入力のみ項目直下に赤字（.field-error）</t>
         </is>
       </c>
     </row>
@@ -848,7 +912,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>W-系メッセージはモーダルで「はい／いいえ」</t>
+          <t>モーダル（ConfirmDialog）で「キャンセル」と実行ボタン（承認する／差戻す／却下する／取り下げる／無効化する／削除する）。承認・差戻し・却下はコメント入力欄（500 文字以内、差戻し・却下は必須）付き。申請の提出は確認なし</t>
         </is>
       </c>
     </row>
@@ -860,7 +924,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>I-系メッセージは成功アラート（.alert-ok：緑字・淡緑背景）で表示。補足案内は情報アラート（.alert-info：紺字・淡青背景）</t>
+          <t>成功メッセージは成功アラート（.alert-ok：緑字・淡緑背景）で表示。補足案内は情報アラート（.alert-info：紺字・淡青背景）</t>
         </is>
       </c>
     </row>
@@ -872,7 +936,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>API呼び出し中はボタンを非活性にし、二重送信を防ぐ</t>
+          <t>API呼び出し中はボタンを非活性にし、二重送信を防ぐ。一覧の読み込み中は「読み込み中…」を表示</t>
         </is>
       </c>
     </row>
@@ -891,12 +955,24 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>メニューの無効表示（初期パスワード時）</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>mustChangePassword=true の間、左メニューの各グループ（見出し・項目）を透明度40%（opacity .4）で薄く表示し、クリックできない状態（pointer-events none）にする。メニューの上部に案内文「パスワードを変更するとメニューが使えるようになります。」（.lock-note：12px・補助文字色・淡青背景・角丸8px）を表示する。ヘッダー（通知ベル・パスワード変更・ログアウト）は無効にしない。パスワード変更後はログインし直すため、通常の表示に戻る（SCR-007）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>共通部品</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>ボタン：通常（.btn：紺）・補助（.btn-ghost：枠線のみ）。入力欄：枠線 #d5dbe8、フォーカス時に紺の枠。補助説明は .hint（12px・補助文字色）。角丸 8px</t>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ボタン：通常（.btn：紺）・補助（.btn-ghost：枠線のみ）・危険（.btn-danger）。状態バッジ（StatusBadge）：申請状態（下書き＝灰／承認待ち＝青／差戻し＝橙／却下＝赤／承認済み＝緑／取下げ＝灰）と承認ステップ状態（承認待ち＝青／承認＝緑／差戻し＝橙／却下＝赤／処理なし＝灰）を色分け表示する（「処理なし」は、取下げ・差戻し・却下で打ち切られ未処理のまま残った段）。ユーザー状態は在籍＝緑・無効＝灰のバッジ。入力欄：枠線 #d5dbe8、フォーカス時に紺の枠。補助説明は .hint（12px・補助文字色）。角丸 8px</t>
         </is>
       </c>
     </row>
@@ -912,11 +988,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -952,12 +1028,12 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>ホーム</t>
+          <t>打刻・勤怠</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>SCR-101</t>
+          <t>/home（SCR-101〜103）</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -979,12 +1055,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>打刻</t>
+          <t>申請</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>SCR-102</t>
+          <t>/requests（SCR-104〜106、SCR-109）</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1006,12 +1082,12 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>月次勤怠</t>
+          <t>休暇残日数</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>SCR-103</t>
+          <t>/leave（SCR-107）</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -1033,12 +1109,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>休暇申請</t>
+          <t>通知</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SCR-105</t>
+          <t>/notifications（SCR-108）</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -1060,17 +1136,17 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>申請一覧</t>
+          <t>承認待ち</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>SCR-106</t>
+          <t>/approvals（SCR-201, 301）</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1087,17 +1163,17 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>休暇残日数</t>
+          <t>部下の勤怠集計</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>SCR-107</t>
+          <t>/manager/summary（SCR-203）</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1107,19 +1183,19 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>承認待ち</t>
+          <t>月次集計</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>SCR-201</t>
+          <t>/admin/reports（SCR-306）</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1129,7 +1205,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1141,12 +1217,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>部下の勤怠</t>
+          <t>ユーザー管理</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>SCR-203</t>
+          <t>/admin/users（SCR-302）</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -1156,24 +1232,24 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>最終承認</t>
+          <t>休暇付与</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>SCR-301</t>
+          <t>/admin/leave-grants（SCR-305）</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1195,12 +1271,12 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ユーザー管理</t>
+          <t>休暇種別</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SCR-302</t>
+          <t>/admin/leave-types（SCR-303）</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1222,12 +1298,12 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>休暇種別</t>
+          <t>祝日・会社休日</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>SCR-303</t>
+          <t>/admin/holidays（SCR-304）</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1249,22 +1325,22 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>祝日</t>
+          <t>パスワード変更（ヘッダー）</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SCR-304</t>
+          <t>/password（SCR-007）</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1276,90 +1352,16 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>休暇付与</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>SCR-305</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>※左メニューの見出しは「勤怠」「承認」「管理」。通知メニューには未読件数のバッジを表示する。ヘッダーにはパスワード変更・ログアウトを表示する。</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>月次集計</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>SCR-306</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>パスワード変更</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>SCR-007</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>※現行実装のヘッダーに出るメニューはホームとパスワード変更。他のメニューは各画面の実装時にヘッダーへ追加する。</t>
-        </is>
-      </c>
+      <c r="A15" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1400,7 +1402,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>ログイン画面以外へのアクセスはSCR-001へリダイレクト</t>
+          <t>ログイン画面以外（認証が必要な画面）へのアクセスは SCR-001（/login）へリダイレクト</t>
         </is>
       </c>
     </row>
@@ -1412,19 +1414,19 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>API が 401 を返したらログイン情報（トークン・利用者情報）を破棄してログイン画面へ自動で戻る（メッセージ表示）。トークン有効期間は 2 時間</t>
+          <t>API が 401 を返したらログイン情報（トークン・利用者情報）を破棄してログイン画面へ自動で戻る（メッセージ表示なし）。401 はトークン期限切れ・不正のほか、ユーザーの無効化・パスワード変更後の旧トークンでも発生する。トークン有効期間は 2 時間</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>権限なし</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>メニュー非表示に加え、API は 403（E-010）を返す。権限エラー専用画面は未実装</t>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>ロールが合わない画面の URL は /home へリダイレクトする（メニューも非表示）。API は 403（E-010）を返す。権限エラー専用画面は未実装</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1438,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Vue Router。ルートのメタ情報 requiresAuth で未ログインを /login へ誘導（ガード）。ロール別の画面制御は画面追加時に拡張する</t>
+          <t>Vue Router。ルートのメタ情報 requiresAuth（未ログインを /login へ誘導）と roles（ロール別の画面制御）で判定するガードを beforeEach に設定。画面は遅延読み込み。未定義の URL は /home へ</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1462,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>mustChangePassword が true の間は /password（SCR-007）以外の認証必須画面へ入れず、/password へ誘導する（ルーターガード）。サーバー側での強制は未実装のため、API を直接呼べば他の機能も利用できる（既知の課題）</t>
+          <t>mustChangePassword が true の間は /password（SCR-007）以外の認証必須画面へ入れず、/password へ誘導する（ルーターガード）。サーバー側でも /api/auth/password 以外の API を 403（E-019）で拒否する。パスワード変更に成功したらトークンを破棄してログイン画面へ戻る。この間、左メニューは無効表示（薄く表示してクリック不可）にして、案内文「パスワードを変更するとメニューが使えるようになります。」を表示する（AppLayout）。ヘッダーの通知ベル・パスワード変更・ログアウトは操作できる</t>
         </is>
       </c>
     </row>
